--- a/Data/CSV/StageMove.xlsx
+++ b/Data/CSV/StageMove.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Class\VocationalSchoolData\Programing\SpringContest\SpringContest_26\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64C0736-E9B1-4F56-AE35-6A34919A90DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D47214D-B7FF-441E-ACD3-62EAE2B79DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5200" yWindow="2930" windowWidth="19200" windowHeight="11180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -504,7 +504,7 @@
       <c r="V2" s="1">
         <v>0</v>
       </c>
-      <c r="W2" s="2">
+      <c r="W2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -548,7 +548,7 @@
       <c r="V3" s="1">
         <v>2</v>
       </c>
-      <c r="W3" s="2">
+      <c r="W3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -556,7 +556,7 @@
       <c r="A4" s="1">
         <v>0</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1">
@@ -571,7 +571,7 @@
       <c r="M4" s="1">
         <v>0</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="R4" s="1">
         <v>0</v>
       </c>
       <c r="S4" s="1">
@@ -580,7 +580,7 @@
       <c r="U4" s="1">
         <v>0</v>
       </c>
-      <c r="W4" s="2">
+      <c r="W4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -594,6 +594,9 @@
       <c r="G5" s="1">
         <v>0</v>
       </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
       <c r="K5" s="1">
         <v>0</v>
       </c>
@@ -606,7 +609,10 @@
       <c r="S5" s="1">
         <v>0</v>
       </c>
-      <c r="W5" s="2">
+      <c r="U5" s="1">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -620,12 +626,6 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
       <c r="K6" s="1">
         <v>0</v>
       </c>
@@ -638,13 +638,7 @@
       <c r="S6" s="1">
         <v>0</v>
       </c>
-      <c r="U6" s="1">
-        <v>0</v>
-      </c>
-      <c r="V6" s="1">
-        <v>0</v>
-      </c>
-      <c r="W6" s="2">
+      <c r="W6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -700,7 +694,7 @@
       <c r="V7" s="1">
         <v>0</v>
       </c>
-      <c r="W7" s="2">
+      <c r="W7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -726,7 +720,7 @@
       <c r="S8" s="1">
         <v>0</v>
       </c>
-      <c r="W8" s="2">
+      <c r="W8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -764,7 +758,7 @@
       <c r="U9" s="1">
         <v>0</v>
       </c>
-      <c r="W9" s="2">
+      <c r="W9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -781,9 +775,6 @@
       <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
       <c r="K10" s="1">
         <v>0</v>
       </c>
@@ -799,10 +790,7 @@
       <c r="R10" s="1">
         <v>0</v>
       </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="W10" s="2">
+      <c r="W10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -816,6 +804,9 @@
       <c r="C11" s="1">
         <v>0</v>
       </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
@@ -834,13 +825,16 @@
       <c r="O11" s="1">
         <v>0</v>
       </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
       <c r="U11" s="1">
         <v>0</v>
       </c>
       <c r="V11" s="1">
         <v>0</v>
       </c>
-      <c r="W11" s="2">
+      <c r="W11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -908,7 +902,7 @@
       <c r="V12" s="1">
         <v>0</v>
       </c>
-      <c r="W12" s="2">
+      <c r="W12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1590,6 +1584,9 @@
       <c r="S29" s="1">
         <v>0</v>
       </c>
+      <c r="V29" s="1">
+        <v>2</v>
+      </c>
       <c r="W29" s="2">
         <v>0</v>
       </c>
@@ -1631,9 +1628,6 @@
       <c r="U30" s="1">
         <v>0</v>
       </c>
-      <c r="V30" s="1">
-        <v>2</v>
-      </c>
       <c r="W30" s="2">
         <v>0</v>
       </c>
@@ -1642,6 +1636,9 @@
       <c r="A31" s="1">
         <v>0</v>
       </c>
+      <c r="B31" s="1">
+        <v>1</v>
+      </c>
       <c r="K31" s="1">
         <v>0</v>
       </c>
@@ -1659,9 +1656,6 @@
       <c r="A32" s="1">
         <v>0</v>
       </c>
-      <c r="B32" s="1">
-        <v>1</v>
-      </c>
       <c r="C32" s="1">
         <v>0</v>
       </c>
@@ -1744,6 +1738,9 @@
       <c r="C34" s="1">
         <v>0</v>
       </c>
+      <c r="H34" s="1">
+        <v>2</v>
+      </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
@@ -1790,9 +1787,6 @@
       </c>
       <c r="G35" s="1">
         <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>2</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>

--- a/Data/CSV/StageMove.xlsx
+++ b/Data/CSV/StageMove.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Class\VocationalSchoolData\Programing\SpringContest\SpringContest_26\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D47214D-B7FF-441E-ACD3-62EAE2B79DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42BFBB9-2F7D-43E7-A703-0A503CF39284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5200" yWindow="2930" windowWidth="19200" windowHeight="11180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>移動ステージ１(前)</t>
   </si>
@@ -36,10 +36,41 @@
     <t>移動ステージ3(前)</t>
   </si>
   <si>
-    <t>移動ステージ１(後ろ)</t>
+    <t>移動ステージ3(奥)</t>
+    <rPh sb="8" eb="9">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>移動ステージ２(後ろ)</t>
+    <t>移動ステージ２(奥)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動ステージ１(奥)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動ステージ4(奥)</t>
+    <rPh sb="8" eb="9">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動ステージ4(前)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動ステージ5(前)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動ステージ5(奥)</t>
+    <rPh sb="8" eb="9">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -424,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:W72"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="22" width="2.58203125" style="1"/>
@@ -437,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -1390,6 +1421,9 @@
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="M25" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="1">
@@ -1883,6 +1917,1104 @@
       <c r="W36" s="2">
         <v>0</v>
       </c>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="A37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23">
+      <c r="A38" s="1">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1">
+        <v>0</v>
+      </c>
+      <c r="T38" s="1">
+        <v>0</v>
+      </c>
+      <c r="U38" s="1">
+        <v>0</v>
+      </c>
+      <c r="V38" s="1">
+        <v>0</v>
+      </c>
+      <c r="W38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" s="1">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>0</v>
+      </c>
+      <c r="R39" s="1">
+        <v>3</v>
+      </c>
+      <c r="S39" s="1">
+        <v>0</v>
+      </c>
+      <c r="T39" s="1">
+        <v>0</v>
+      </c>
+      <c r="U39" s="1">
+        <v>0</v>
+      </c>
+      <c r="V39" s="1">
+        <v>0</v>
+      </c>
+      <c r="W39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" s="1">
+        <v>0</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
+        <v>0</v>
+      </c>
+      <c r="O40" s="1">
+        <v>0</v>
+      </c>
+      <c r="P40" s="1">
+        <v>0</v>
+      </c>
+      <c r="T40" s="1">
+        <v>0</v>
+      </c>
+      <c r="U40" s="1">
+        <v>0</v>
+      </c>
+      <c r="V40" s="1">
+        <v>0</v>
+      </c>
+      <c r="W40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23">
+      <c r="A41" s="1">
+        <v>0</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>3</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0</v>
+      </c>
+      <c r="U41" s="1">
+        <v>0</v>
+      </c>
+      <c r="V41" s="1">
+        <v>0</v>
+      </c>
+      <c r="W41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="1">
+        <v>0</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1">
+        <v>0</v>
+      </c>
+      <c r="W42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="W43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" s="1">
+        <v>0</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>2</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" s="1">
+        <v>0</v>
+      </c>
+      <c r="B45" s="1">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>0</v>
+      </c>
+      <c r="S45" s="1">
+        <v>0</v>
+      </c>
+      <c r="T45" s="1">
+        <v>2</v>
+      </c>
+      <c r="V45" s="1">
+        <v>0</v>
+      </c>
+      <c r="W45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23">
+      <c r="A46" s="1">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1">
+        <v>0</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1">
+        <v>0</v>
+      </c>
+      <c r="U46" s="1">
+        <v>0</v>
+      </c>
+      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="W46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23">
+      <c r="A47" s="1">
+        <v>0</v>
+      </c>
+      <c r="B47" s="1">
+        <v>0</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1">
+        <v>0</v>
+      </c>
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>1</v>
+      </c>
+      <c r="T47" s="1">
+        <v>0</v>
+      </c>
+      <c r="U47" s="1">
+        <v>0</v>
+      </c>
+      <c r="V47" s="1">
+        <v>0</v>
+      </c>
+      <c r="W47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23">
+      <c r="A48" s="1">
+        <v>0</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1">
+        <v>0</v>
+      </c>
+      <c r="O48" s="1">
+        <v>0</v>
+      </c>
+      <c r="P48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>0</v>
+      </c>
+      <c r="R48" s="1">
+        <v>0</v>
+      </c>
+      <c r="S48" s="1">
+        <v>0</v>
+      </c>
+      <c r="T48" s="1">
+        <v>0</v>
+      </c>
+      <c r="U48" s="1">
+        <v>0</v>
+      </c>
+      <c r="V48" s="1">
+        <v>0</v>
+      </c>
+      <c r="W48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23">
+      <c r="A49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23">
+      <c r="A50" s="1">
+        <v>0</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1">
+        <v>0</v>
+      </c>
+      <c r="U50" s="1">
+        <v>0</v>
+      </c>
+      <c r="V50" s="1">
+        <v>0</v>
+      </c>
+      <c r="W50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23">
+      <c r="A51" s="1">
+        <v>0</v>
+      </c>
+      <c r="B51" s="1">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0</v>
+      </c>
+      <c r="O51" s="1">
+        <v>0</v>
+      </c>
+      <c r="P51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>3</v>
+      </c>
+      <c r="S51" s="1">
+        <v>0</v>
+      </c>
+      <c r="T51" s="1">
+        <v>0</v>
+      </c>
+      <c r="U51" s="1">
+        <v>0</v>
+      </c>
+      <c r="V51" s="1">
+        <v>0</v>
+      </c>
+      <c r="W51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23">
+      <c r="A52" s="1">
+        <v>0</v>
+      </c>
+      <c r="B52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>2</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0</v>
+      </c>
+      <c r="O52" s="1">
+        <v>0</v>
+      </c>
+      <c r="U52" s="1">
+        <v>0</v>
+      </c>
+      <c r="V52" s="1">
+        <v>0</v>
+      </c>
+      <c r="W52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23">
+      <c r="A53" s="1">
+        <v>0</v>
+      </c>
+      <c r="B53" s="1">
+        <v>0</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0</v>
+      </c>
+      <c r="O53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="S53" s="1">
+        <v>0</v>
+      </c>
+      <c r="U53" s="1">
+        <v>0</v>
+      </c>
+      <c r="V53" s="1">
+        <v>0</v>
+      </c>
+      <c r="W53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23">
+      <c r="A54" s="1">
+        <v>0</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="K54" s="1">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>0</v>
+      </c>
+      <c r="O54" s="1">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+      <c r="U54" s="1">
+        <v>0</v>
+      </c>
+      <c r="V54" s="1">
+        <v>0</v>
+      </c>
+      <c r="W54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23">
+      <c r="A55" s="1">
+        <v>0</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="1">
+        <v>3</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>0</v>
+      </c>
+      <c r="O55" s="1">
+        <v>0</v>
+      </c>
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+      <c r="T55" s="1">
+        <v>0</v>
+      </c>
+      <c r="U55" s="1">
+        <v>0</v>
+      </c>
+      <c r="V55" s="1">
+        <v>0</v>
+      </c>
+      <c r="W55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23">
+      <c r="A56" s="1">
+        <v>0</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0</v>
+      </c>
+      <c r="O56" s="1">
+        <v>1</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="V56" s="1">
+        <v>0</v>
+      </c>
+      <c r="W56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23">
+      <c r="A57" s="1">
+        <v>0</v>
+      </c>
+      <c r="B57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0</v>
+      </c>
+      <c r="O57" s="1">
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+      <c r="T57" s="1">
+        <v>0</v>
+      </c>
+      <c r="U57" s="1">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1">
+        <v>0</v>
+      </c>
+      <c r="W57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23">
+      <c r="A58" s="1">
+        <v>0</v>
+      </c>
+      <c r="B58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <v>0</v>
+      </c>
+      <c r="O58" s="1">
+        <v>0</v>
+      </c>
+      <c r="U58" s="1">
+        <v>0</v>
+      </c>
+      <c r="V58" s="1">
+        <v>0</v>
+      </c>
+      <c r="W58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23">
+      <c r="A59" s="1">
+        <v>0</v>
+      </c>
+      <c r="B59" s="1">
+        <v>0</v>
+      </c>
+      <c r="C59" s="1">
+        <v>0</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1">
+        <v>0</v>
+      </c>
+      <c r="O59" s="1">
+        <v>0</v>
+      </c>
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
+      <c r="T59" s="1">
+        <v>2</v>
+      </c>
+      <c r="U59" s="1">
+        <v>0</v>
+      </c>
+      <c r="V59" s="1">
+        <v>0</v>
+      </c>
+      <c r="W59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23">
+      <c r="A60" s="1">
+        <v>0</v>
+      </c>
+      <c r="B60" s="1">
+        <v>0</v>
+      </c>
+      <c r="C60" s="1">
+        <v>0</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0</v>
+      </c>
+      <c r="N60" s="1">
+        <v>0</v>
+      </c>
+      <c r="O60" s="1">
+        <v>0</v>
+      </c>
+      <c r="P60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>0</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0</v>
+      </c>
+      <c r="S60" s="1">
+        <v>0</v>
+      </c>
+      <c r="T60" s="1">
+        <v>0</v>
+      </c>
+      <c r="U60" s="1">
+        <v>0</v>
+      </c>
+      <c r="V60" s="1">
+        <v>0</v>
+      </c>
+      <c r="W60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23">
+      <c r="W62" s="1"/>
+    </row>
+    <row r="63" spans="1:23">
+      <c r="W63" s="1"/>
+    </row>
+    <row r="64" spans="1:23">
+      <c r="W64" s="1"/>
+    </row>
+    <row r="65" spans="23:23">
+      <c r="W65" s="1"/>
+    </row>
+    <row r="66" spans="23:23">
+      <c r="W66" s="1"/>
+    </row>
+    <row r="67" spans="23:23">
+      <c r="W67" s="1"/>
+    </row>
+    <row r="68" spans="23:23">
+      <c r="W68" s="1"/>
+    </row>
+    <row r="69" spans="23:23">
+      <c r="W69" s="1"/>
+    </row>
+    <row r="70" spans="23:23">
+      <c r="W70" s="1"/>
+    </row>
+    <row r="71" spans="23:23">
+      <c r="W71" s="1"/>
+    </row>
+    <row r="72" spans="23:23">
+      <c r="W72" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Data/CSV/StageMove.xlsx
+++ b/Data/CSV/StageMove.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Class\VocationalSchoolData\Programing\SpringContest\SpringContest_26\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42BFBB9-2F7D-43E7-A703-0A503CF39284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469903D3-D6FA-4008-AE54-0D0475EC8411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,50 +25,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="2">
   <si>
-    <t>移動ステージ１(前)</t>
-  </si>
-  <si>
-    <t>移動ステージ２(前)</t>
-  </si>
-  <si>
-    <t>移動ステージ3(前)</t>
-  </si>
-  <si>
-    <t>移動ステージ3(奥)</t>
-    <rPh sb="8" eb="9">
-      <t>オク</t>
+    <t>回で最短攻略</t>
+    <rPh sb="0" eb="1">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウリャク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>移動ステージ２(奥)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>移動ステージ１(奥)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>移動ステージ4(奥)</t>
-    <rPh sb="8" eb="9">
-      <t>オク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>移動ステージ4(前)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>移動ステージ5(前)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>移動ステージ5(奥)</t>
-    <rPh sb="8" eb="9">
-      <t>オク</t>
+    <t>回で最短攻略</t>
+    <rPh sb="0" eb="1">
+      <t>カイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -134,7 +105,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <font>
         <color theme="0"/>
@@ -179,8 +150,23 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF8A0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF8A0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -455,20 +441,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:W84"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="22" width="2.58203125" style="1"/>
+    <col min="1" max="1" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="2.58203125" style="1"/>
+    <col min="13" max="13" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="2.58203125" style="1"/>
+    <col min="18" max="18" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="2.58203125" style="1"/>
     <col min="23" max="23" width="2.58203125" style="2"/>
     <col min="24" max="16384" width="2.58203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>5</v>
+      <c r="A1" s="1">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="1">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -552,32 +549,56 @@
       <c r="D3" s="1">
         <v>0</v>
       </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2</v>
+      </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+      <c r="T3" s="1">
         <v>2</v>
       </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-      <c r="M3" s="1">
-        <v>0</v>
-      </c>
-      <c r="N3" s="1">
-        <v>0</v>
-      </c>
-      <c r="O3" s="1">
-        <v>0</v>
-      </c>
-      <c r="P3" s="1">
-        <v>0</v>
-      </c>
       <c r="U3" s="1">
         <v>0</v>
       </c>
       <c r="V3" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -587,15 +608,15 @@
       <c r="A4" s="1">
         <v>0</v>
       </c>
+      <c r="B4" s="1">
+        <v>4</v>
+      </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
       <c r="K4" s="1">
         <v>0</v>
       </c>
@@ -608,8 +629,8 @@
       <c r="S4" s="1">
         <v>0</v>
       </c>
-      <c r="U4" s="1">
-        <v>0</v>
+      <c r="V4" s="1">
+        <v>4</v>
       </c>
       <c r="W4" s="1">
         <v>0</v>
@@ -619,29 +640,20 @@
       <c r="A5" s="1">
         <v>0</v>
       </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
       <c r="K5" s="1">
         <v>0</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
       </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
       <c r="S5" s="1">
         <v>0</v>
       </c>
-      <c r="U5" s="1">
-        <v>0</v>
+      <c r="V5" s="1">
+        <v>4</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
@@ -651,23 +663,47 @@
       <c r="A6" s="1">
         <v>0</v>
       </c>
+      <c r="D6" s="1">
+        <v>4</v>
+      </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
+      <c r="H6" s="1">
+        <v>4</v>
+      </c>
+      <c r="I6" s="1">
+        <v>4</v>
+      </c>
       <c r="K6" s="1">
         <v>0</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
       </c>
+      <c r="N6" s="1">
+        <v>4</v>
+      </c>
+      <c r="O6" s="1">
+        <v>4</v>
+      </c>
+      <c r="P6" s="1">
+        <v>4</v>
+      </c>
       <c r="Q6" s="1">
         <v>0</v>
       </c>
       <c r="S6" s="1">
         <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>4</v>
+      </c>
+      <c r="V6" s="1">
+        <v>4</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
@@ -692,12 +728,6 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
       <c r="K7" s="1">
         <v>0</v>
       </c>
@@ -719,11 +749,8 @@
       <c r="S7" s="1">
         <v>0</v>
       </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>0</v>
+      <c r="T7" s="1">
+        <v>4</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
@@ -745,11 +772,26 @@
       <c r="M8" s="1">
         <v>0</v>
       </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
       <c r="Q8" s="1">
         <v>0</v>
       </c>
       <c r="S8" s="1">
         <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>4</v>
+      </c>
+      <c r="U8" s="1">
+        <v>4</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
@@ -768,8 +810,11 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="1">
-        <v>0</v>
+      <c r="G9" s="1">
+        <v>4</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -783,10 +828,13 @@
       <c r="O9" s="1">
         <v>0</v>
       </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
       <c r="Q9" s="1">
         <v>0</v>
       </c>
-      <c r="U9" s="1">
+      <c r="S9" s="1">
         <v>0</v>
       </c>
       <c r="W9" s="1">
@@ -803,9 +851,6 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
       <c r="K10" s="1">
         <v>0</v>
       </c>
@@ -813,13 +858,19 @@
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
       </c>
       <c r="Q10" s="1">
         <v>0</v>
       </c>
-      <c r="R10" s="1">
-        <v>0</v>
+      <c r="S10" s="1">
+        <v>4</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
@@ -835,14 +886,17 @@
       <c r="C11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>4</v>
       </c>
       <c r="J11" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -856,14 +910,14 @@
       <c r="O11" s="1">
         <v>0</v>
       </c>
-      <c r="T11" s="1">
-        <v>0</v>
-      </c>
-      <c r="U11" s="1">
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
         <v>0</v>
       </c>
       <c r="V11" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
@@ -938,11 +992,17 @@
       </c>
     </row>
     <row r="13" spans="1:23">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>4</v>
+      <c r="M13" s="1">
+        <v>8</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -1017,22 +1077,52 @@
       <c r="A15" s="1">
         <v>0</v>
       </c>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
       <c r="C15" s="1">
         <v>0</v>
       </c>
+      <c r="E15" s="1">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1">
+        <v>4</v>
+      </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
       <c r="K15" s="1">
         <v>0</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
       </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
       <c r="O15" s="1">
         <v>0</v>
       </c>
+      <c r="Q15" s="1">
+        <v>4</v>
+      </c>
+      <c r="R15" s="1">
+        <v>3</v>
+      </c>
+      <c r="S15" s="1">
+        <v>4</v>
+      </c>
       <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
         <v>0</v>
       </c>
       <c r="W15" s="2">
@@ -1043,22 +1133,37 @@
       <c r="A16" s="1">
         <v>0</v>
       </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
       <c r="C16" s="1">
         <v>0</v>
       </c>
+      <c r="F16" s="1">
+        <v>3</v>
+      </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
       <c r="K16" s="1">
         <v>0</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
       </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
       <c r="O16" s="1">
         <v>0</v>
       </c>
       <c r="U16" s="1">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
         <v>0</v>
       </c>
       <c r="W16" s="2">
@@ -1075,14 +1180,11 @@
       <c r="D17" s="1">
         <v>0</v>
       </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
       <c r="H17" s="1">
         <v>0</v>
       </c>
-      <c r="I17" s="1">
-        <v>0</v>
+      <c r="J17" s="1">
+        <v>2</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -1090,6 +1192,9 @@
       <c r="M17" s="1">
         <v>0</v>
       </c>
+      <c r="N17" s="1">
+        <v>4</v>
+      </c>
       <c r="O17" s="1">
         <v>0</v>
       </c>
@@ -1097,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="Q17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T17" s="1">
         <v>0</v>
       </c>
-      <c r="U17" s="1">
-        <v>0</v>
+      <c r="V17" s="1">
+        <v>2</v>
       </c>
       <c r="W17" s="2">
         <v>0</v>
@@ -1119,8 +1224,8 @@
       <c r="D18" s="1">
         <v>0</v>
       </c>
-      <c r="E18" s="1">
-        <v>0</v>
+      <c r="F18" s="1">
+        <v>4</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -1131,14 +1236,11 @@
       <c r="M18" s="1">
         <v>0</v>
       </c>
-      <c r="N18" s="1">
-        <v>1</v>
-      </c>
       <c r="P18" s="1">
         <v>0</v>
       </c>
-      <c r="Q18" s="1">
-        <v>0</v>
+      <c r="R18" s="1">
+        <v>4</v>
       </c>
       <c r="T18" s="1">
         <v>0</v>
@@ -1151,18 +1253,9 @@
       <c r="A19" s="1">
         <v>0</v>
       </c>
-      <c r="B19" s="1">
-        <v>0</v>
-      </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1">
-        <v>3</v>
-      </c>
       <c r="H19" s="1">
         <v>0</v>
       </c>
@@ -1172,20 +1265,14 @@
       <c r="M19" s="1">
         <v>0</v>
       </c>
-      <c r="N19" s="1">
-        <v>0</v>
-      </c>
       <c r="P19" s="1">
         <v>0</v>
       </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1">
-        <v>3</v>
-      </c>
       <c r="T19" s="1">
         <v>0</v>
+      </c>
+      <c r="V19" s="1">
+        <v>4</v>
       </c>
       <c r="W19" s="2">
         <v>0</v>
@@ -1195,8 +1282,14 @@
       <c r="A20" s="1">
         <v>0</v>
       </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -1207,8 +1300,14 @@
       <c r="M20" s="1">
         <v>0</v>
       </c>
-      <c r="Q20" s="1">
-        <v>0</v>
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>4</v>
+      </c>
+      <c r="S20" s="1">
+        <v>4</v>
       </c>
       <c r="T20" s="1">
         <v>0</v>
@@ -1221,28 +1320,10 @@
       <c r="A21" s="1">
         <v>0</v>
       </c>
-      <c r="B21" s="1">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
       <c r="K21" s="1">
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1">
         <v>0</v>
       </c>
       <c r="W21" s="2">
@@ -1259,15 +1340,12 @@
       <c r="C22" s="1">
         <v>0</v>
       </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
       <c r="K22" s="1">
         <v>0</v>
       </c>
@@ -1278,15 +1356,15 @@
         <v>0</v>
       </c>
       <c r="O22" s="1">
-        <v>0</v>
-      </c>
-      <c r="S22" s="1">
-        <v>0</v>
-      </c>
-      <c r="T22" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="R22" s="1">
+        <v>4</v>
       </c>
       <c r="U22" s="1">
+        <v>4</v>
+      </c>
+      <c r="V22" s="1">
         <v>0</v>
       </c>
       <c r="W22" s="2">
@@ -1309,14 +1387,11 @@
       <c r="G23" s="1">
         <v>0</v>
       </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -1330,20 +1405,26 @@
       <c r="O23" s="1">
         <v>0</v>
       </c>
+      <c r="P23" s="1">
+        <v>4</v>
+      </c>
       <c r="Q23" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="R23" s="1">
+        <v>4</v>
       </c>
       <c r="S23" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T23" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U23" s="1">
         <v>0</v>
       </c>
       <c r="V23" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W23" s="2">
         <v>0</v>
@@ -1418,11 +1499,17 @@
       </c>
     </row>
     <row r="25" spans="1:23">
-      <c r="A25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>3</v>
+      <c r="A25" s="1">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1">
+        <v>4</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -1530,6 +1617,15 @@
       <c r="P27" s="1">
         <v>0</v>
       </c>
+      <c r="Q27" s="1">
+        <v>4</v>
+      </c>
+      <c r="R27" s="1">
+        <v>4</v>
+      </c>
+      <c r="S27" s="1">
+        <v>4</v>
+      </c>
       <c r="T27" s="1">
         <v>0</v>
       </c>
@@ -1554,13 +1650,16 @@
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>4</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
@@ -1600,6 +1699,9 @@
       <c r="I29" s="1">
         <v>0</v>
       </c>
+      <c r="J29" s="1">
+        <v>4</v>
+      </c>
       <c r="K29" s="1">
         <v>0</v>
       </c>
@@ -1613,10 +1715,13 @@
         <v>0</v>
       </c>
       <c r="Q29" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S29" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="U29" s="1">
+        <v>4</v>
       </c>
       <c r="V29" s="1">
         <v>2</v>
@@ -1673,14 +1778,23 @@
       <c r="B31" s="1">
         <v>1</v>
       </c>
+      <c r="F31" s="1">
+        <v>4</v>
+      </c>
       <c r="K31" s="1">
         <v>0</v>
       </c>
       <c r="M31" s="1">
         <v>0</v>
       </c>
+      <c r="N31" s="1">
+        <v>4</v>
+      </c>
+      <c r="O31" s="1">
+        <v>4</v>
+      </c>
       <c r="R31" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W31" s="2">
         <v>0</v>
@@ -1690,11 +1804,14 @@
       <c r="A32" s="1">
         <v>0</v>
       </c>
+      <c r="B32" s="1">
+        <v>4</v>
+      </c>
       <c r="C32" s="1">
         <v>0</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
@@ -1708,14 +1825,11 @@
       <c r="M32" s="1">
         <v>0</v>
       </c>
-      <c r="N32" s="1">
-        <v>1</v>
-      </c>
       <c r="O32" s="1">
         <v>0</v>
       </c>
       <c r="R32" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U32" s="1">
         <v>0</v>
@@ -1738,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -1793,6 +1907,12 @@
       <c r="O34" s="1">
         <v>0</v>
       </c>
+      <c r="Q34" s="1">
+        <v>4</v>
+      </c>
+      <c r="S34" s="1">
+        <v>4</v>
+      </c>
       <c r="U34" s="1">
         <v>0</v>
       </c>
@@ -1813,6 +1933,9 @@
       <c r="C35" s="1">
         <v>0</v>
       </c>
+      <c r="D35" s="1">
+        <v>4</v>
+      </c>
       <c r="E35" s="1">
         <v>0</v>
       </c>
@@ -1821,6 +1944,9 @@
       </c>
       <c r="G35" s="1">
         <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>4</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
@@ -1919,11 +2045,17 @@
       </c>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>6</v>
+      <c r="A37" s="1">
+        <v>4</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1">
+        <v>4</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:23">
@@ -2140,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
@@ -2156,6 +2288,15 @@
       </c>
       <c r="N42" s="1">
         <v>0</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>4</v>
+      </c>
+      <c r="R42" s="1">
+        <v>4</v>
+      </c>
+      <c r="S42" s="1">
+        <v>4</v>
       </c>
       <c r="V42" s="1">
         <v>0</v>
@@ -2172,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
@@ -2182,6 +2323,9 @@
       </c>
       <c r="M43" s="1">
         <v>0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>4</v>
       </c>
       <c r="W43" s="1">
         <v>0</v>
@@ -2192,19 +2336,19 @@
         <v>0</v>
       </c>
       <c r="B44" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="F44" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H44" s="1">
         <v>2</v>
       </c>
       <c r="J44" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K44" s="1">
         <v>0</v>
@@ -2224,10 +2368,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I45" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J45" s="1">
         <v>0</v>
@@ -2243,6 +2387,9 @@
       </c>
       <c r="Q45" s="1">
         <v>0</v>
+      </c>
+      <c r="R45" s="1">
+        <v>4</v>
       </c>
       <c r="S45" s="1">
         <v>0</v>
@@ -2268,10 +2415,10 @@
         <v>0</v>
       </c>
       <c r="D46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
@@ -2296,6 +2443,9 @@
       </c>
       <c r="Q46" s="1">
         <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>4</v>
       </c>
       <c r="S46" s="1">
         <v>0</v>
@@ -2327,10 +2477,10 @@
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -2357,7 +2507,13 @@
         <v>0</v>
       </c>
       <c r="Q47" s="1">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="R47" s="1">
+        <v>4</v>
+      </c>
+      <c r="S47" s="1">
+        <v>4</v>
       </c>
       <c r="T47" s="1">
         <v>0</v>
@@ -2441,11 +2597,17 @@
       </c>
     </row>
     <row r="49" spans="1:23">
-      <c r="A49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M49" s="1" t="s">
-        <v>9</v>
+      <c r="A49" s="1">
+        <v>11</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M49" s="1">
+        <v>11</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:23">
@@ -2529,6 +2691,15 @@
       <c r="D51" s="1">
         <v>0</v>
       </c>
+      <c r="E51" s="1">
+        <v>4</v>
+      </c>
+      <c r="F51" s="1">
+        <v>4</v>
+      </c>
+      <c r="G51" s="1">
+        <v>4</v>
+      </c>
       <c r="H51" s="1">
         <v>0</v>
       </c>
@@ -2582,6 +2753,9 @@
       <c r="B52" s="1">
         <v>0</v>
       </c>
+      <c r="F52" s="1">
+        <v>4</v>
+      </c>
       <c r="H52" s="1">
         <v>2</v>
       </c>
@@ -2645,10 +2819,10 @@
         <v>0</v>
       </c>
       <c r="Q53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U53" s="1">
         <v>0</v>
@@ -2708,6 +2882,9 @@
       <c r="A55" s="1">
         <v>0</v>
       </c>
+      <c r="C55" s="1">
+        <v>4</v>
+      </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
@@ -2723,6 +2900,9 @@
       <c r="H55" s="1">
         <v>0</v>
       </c>
+      <c r="I55" s="1">
+        <v>4</v>
+      </c>
       <c r="K55" s="1">
         <v>0</v>
       </c>
@@ -2776,11 +2956,8 @@
       <c r="N56" s="1">
         <v>0</v>
       </c>
-      <c r="O56" s="1">
-        <v>1</v>
-      </c>
       <c r="R56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V56" s="1">
         <v>0</v>
@@ -2796,6 +2973,9 @@
       <c r="B57" s="1">
         <v>0</v>
       </c>
+      <c r="D57" s="1">
+        <v>4</v>
+      </c>
       <c r="E57" s="1">
         <v>0</v>
       </c>
@@ -2840,6 +3020,9 @@
       <c r="B58" s="1">
         <v>0</v>
       </c>
+      <c r="I58" s="1">
+        <v>4</v>
+      </c>
       <c r="J58" s="1">
         <v>0</v>
       </c>
@@ -2878,6 +3061,15 @@
       <c r="D59" s="1">
         <v>0</v>
       </c>
+      <c r="E59" s="1">
+        <v>4</v>
+      </c>
+      <c r="F59" s="1">
+        <v>4</v>
+      </c>
+      <c r="G59" s="1">
+        <v>4</v>
+      </c>
       <c r="H59" s="1">
         <v>0</v>
       </c>
@@ -2983,55 +3175,1102 @@
         <v>0</v>
       </c>
     </row>
+    <row r="61" spans="1:23">
+      <c r="A61" s="1">
+        <v>7</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M61" s="1">
+        <v>10</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="62" spans="1:23">
-      <c r="W62" s="1"/>
+      <c r="A62" s="1">
+        <v>0</v>
+      </c>
+      <c r="B62" s="1">
+        <v>0</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
+        <v>0</v>
+      </c>
+      <c r="O62" s="1">
+        <v>0</v>
+      </c>
+      <c r="P62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>0</v>
+      </c>
+      <c r="R62" s="1">
+        <v>0</v>
+      </c>
+      <c r="S62" s="1">
+        <v>0</v>
+      </c>
+      <c r="T62" s="1">
+        <v>0</v>
+      </c>
+      <c r="U62" s="1">
+        <v>0</v>
+      </c>
+      <c r="V62" s="1">
+        <v>0</v>
+      </c>
+      <c r="W62" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="1:23">
-      <c r="W63" s="1"/>
+      <c r="A63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="1">
+        <v>2</v>
+      </c>
+      <c r="K63" s="1">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>0</v>
+      </c>
+      <c r="O63" s="1">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+      <c r="S63" s="1">
+        <v>0</v>
+      </c>
+      <c r="U63" s="1">
+        <v>0</v>
+      </c>
+      <c r="W63" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:23">
-      <c r="W64" s="1"/>
-    </row>
-    <row r="65" spans="23:23">
-      <c r="W65" s="1"/>
-    </row>
-    <row r="66" spans="23:23">
-      <c r="W66" s="1"/>
-    </row>
-    <row r="67" spans="23:23">
-      <c r="W67" s="1"/>
-    </row>
-    <row r="68" spans="23:23">
-      <c r="W68" s="1"/>
-    </row>
-    <row r="69" spans="23:23">
-      <c r="W69" s="1"/>
-    </row>
-    <row r="70" spans="23:23">
-      <c r="W70" s="1"/>
-    </row>
-    <row r="71" spans="23:23">
-      <c r="W71" s="1"/>
-    </row>
-    <row r="72" spans="23:23">
-      <c r="W72" s="1"/>
+      <c r="A64" s="1">
+        <v>0</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
+        <v>0</v>
+      </c>
+      <c r="N64" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>0</v>
+      </c>
+      <c r="R64" s="1">
+        <v>0</v>
+      </c>
+      <c r="S64" s="1">
+        <v>0</v>
+      </c>
+      <c r="U64" s="1">
+        <v>0</v>
+      </c>
+      <c r="W64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23">
+      <c r="A65" s="1">
+        <v>0</v>
+      </c>
+      <c r="B65" s="1">
+        <v>0</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1">
+        <v>4</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="M65" s="1">
+        <v>0</v>
+      </c>
+      <c r="N65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>0</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0</v>
+      </c>
+      <c r="S65" s="1">
+        <v>0</v>
+      </c>
+      <c r="T65" s="1">
+        <v>0</v>
+      </c>
+      <c r="U65" s="1">
+        <v>0</v>
+      </c>
+      <c r="V65" s="1">
+        <v>0</v>
+      </c>
+      <c r="W65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23">
+      <c r="A66" s="1">
+        <v>0</v>
+      </c>
+      <c r="B66" s="1">
+        <v>4</v>
+      </c>
+      <c r="D66" s="1">
+        <v>4</v>
+      </c>
+      <c r="H66" s="1">
+        <v>4</v>
+      </c>
+      <c r="J66" s="1">
+        <v>4</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="M66" s="1">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1">
+        <v>4</v>
+      </c>
+      <c r="S66" s="1">
+        <v>4</v>
+      </c>
+      <c r="W66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23">
+      <c r="A67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="1">
+        <v>4</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="M67" s="1">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
+        <v>4</v>
+      </c>
+      <c r="P67" s="1">
+        <v>4</v>
+      </c>
+      <c r="W67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23">
+      <c r="A68" s="1">
+        <v>0</v>
+      </c>
+      <c r="C68" s="1">
+        <v>4</v>
+      </c>
+      <c r="D68" s="1">
+        <v>4</v>
+      </c>
+      <c r="H68" s="1">
+        <v>4</v>
+      </c>
+      <c r="I68" s="1">
+        <v>4</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>0</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23">
+      <c r="A69" s="1">
+        <v>0</v>
+      </c>
+      <c r="B69" s="1">
+        <v>4</v>
+      </c>
+      <c r="F69" s="1">
+        <v>4</v>
+      </c>
+      <c r="J69" s="1">
+        <v>4</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1">
+        <v>0</v>
+      </c>
+      <c r="N69" s="1">
+        <v>0</v>
+      </c>
+      <c r="O69" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>0</v>
+      </c>
+      <c r="R69" s="1">
+        <v>0</v>
+      </c>
+      <c r="S69" s="1">
+        <v>0</v>
+      </c>
+      <c r="T69" s="1">
+        <v>0</v>
+      </c>
+      <c r="V69" s="1">
+        <v>4</v>
+      </c>
+      <c r="W69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23">
+      <c r="A70" s="1">
+        <v>0</v>
+      </c>
+      <c r="B70" s="1">
+        <v>4</v>
+      </c>
+      <c r="E70" s="1">
+        <v>4</v>
+      </c>
+      <c r="G70" s="1">
+        <v>4</v>
+      </c>
+      <c r="H70" s="1">
+        <v>3</v>
+      </c>
+      <c r="J70" s="1">
+        <v>4</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="M70" s="1">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>0</v>
+      </c>
+      <c r="R70" s="1">
+        <v>0</v>
+      </c>
+      <c r="V70" s="1">
+        <v>4</v>
+      </c>
+      <c r="W70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23">
+      <c r="A71" s="1">
+        <v>0</v>
+      </c>
+      <c r="C71" s="1">
+        <v>4</v>
+      </c>
+      <c r="D71" s="1">
+        <v>4</v>
+      </c>
+      <c r="H71" s="1">
+        <v>4</v>
+      </c>
+      <c r="I71" s="1">
+        <v>4</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1">
+        <v>0</v>
+      </c>
+      <c r="N71" s="1">
+        <v>0</v>
+      </c>
+      <c r="O71" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>0</v>
+      </c>
+      <c r="R71" s="1">
+        <v>0</v>
+      </c>
+      <c r="S71" s="1">
+        <v>3</v>
+      </c>
+      <c r="T71" s="1">
+        <v>4</v>
+      </c>
+      <c r="V71" s="1">
+        <v>4</v>
+      </c>
+      <c r="W71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23">
+      <c r="A72" s="1">
+        <v>0</v>
+      </c>
+      <c r="B72" s="1">
+        <v>0</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>0</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1">
+        <v>0</v>
+      </c>
+      <c r="N72" s="1">
+        <v>0</v>
+      </c>
+      <c r="O72" s="1">
+        <v>0</v>
+      </c>
+      <c r="P72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>0</v>
+      </c>
+      <c r="R72" s="1">
+        <v>0</v>
+      </c>
+      <c r="S72" s="1">
+        <v>0</v>
+      </c>
+      <c r="T72" s="1">
+        <v>0</v>
+      </c>
+      <c r="U72" s="1">
+        <v>0</v>
+      </c>
+      <c r="V72" s="1">
+        <v>0</v>
+      </c>
+      <c r="W72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23">
+      <c r="A73" s="1">
+        <v>5</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M73" s="1">
+        <v>10</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23">
+      <c r="A74" s="1">
+        <v>0</v>
+      </c>
+      <c r="B74" s="1">
+        <v>0</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1">
+        <v>0</v>
+      </c>
+      <c r="M74" s="1">
+        <v>0</v>
+      </c>
+      <c r="N74" s="1">
+        <v>0</v>
+      </c>
+      <c r="O74" s="1">
+        <v>0</v>
+      </c>
+      <c r="P74" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>0</v>
+      </c>
+      <c r="R74" s="1">
+        <v>0</v>
+      </c>
+      <c r="S74" s="1">
+        <v>0</v>
+      </c>
+      <c r="T74" s="1">
+        <v>0</v>
+      </c>
+      <c r="U74" s="1">
+        <v>0</v>
+      </c>
+      <c r="V74" s="1">
+        <v>0</v>
+      </c>
+      <c r="W74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23">
+      <c r="A75" s="1">
+        <v>0</v>
+      </c>
+      <c r="B75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1">
+        <v>0</v>
+      </c>
+      <c r="O75" s="1">
+        <v>3</v>
+      </c>
+      <c r="P75" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>0</v>
+      </c>
+      <c r="R75" s="1">
+        <v>0</v>
+      </c>
+      <c r="T75" s="1">
+        <v>2</v>
+      </c>
+      <c r="U75" s="1">
+        <v>0</v>
+      </c>
+      <c r="V75" s="1">
+        <v>0</v>
+      </c>
+      <c r="W75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23">
+      <c r="A76" s="1">
+        <v>0</v>
+      </c>
+      <c r="B76" s="1">
+        <v>0</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>0</v>
+      </c>
+      <c r="R76" s="1">
+        <v>0</v>
+      </c>
+      <c r="U76" s="1">
+        <v>0</v>
+      </c>
+      <c r="V76" s="1">
+        <v>0</v>
+      </c>
+      <c r="W76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23">
+      <c r="A77" s="1">
+        <v>0</v>
+      </c>
+      <c r="B77" s="1">
+        <v>0</v>
+      </c>
+      <c r="C77" s="1">
+        <v>0</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="F77" s="1">
+        <v>3</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1">
+        <v>4</v>
+      </c>
+      <c r="K77" s="1">
+        <v>0</v>
+      </c>
+      <c r="M77" s="1">
+        <v>0</v>
+      </c>
+      <c r="N77" s="1">
+        <v>0</v>
+      </c>
+      <c r="O77" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>0</v>
+      </c>
+      <c r="R77" s="1">
+        <v>0</v>
+      </c>
+      <c r="T77" s="1">
+        <v>4</v>
+      </c>
+      <c r="U77" s="1">
+        <v>0</v>
+      </c>
+      <c r="V77" s="1">
+        <v>0</v>
+      </c>
+      <c r="W77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23">
+      <c r="A78" s="1">
+        <v>0</v>
+      </c>
+      <c r="D78" s="1">
+        <v>4</v>
+      </c>
+      <c r="I78" s="1">
+        <v>4</v>
+      </c>
+      <c r="J78" s="1">
+        <v>4</v>
+      </c>
+      <c r="K78" s="1">
+        <v>0</v>
+      </c>
+      <c r="M78" s="1">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1">
+        <v>0</v>
+      </c>
+      <c r="O78" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>0</v>
+      </c>
+      <c r="R78" s="1">
+        <v>0</v>
+      </c>
+      <c r="U78" s="1">
+        <v>0</v>
+      </c>
+      <c r="V78" s="1">
+        <v>0</v>
+      </c>
+      <c r="W78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23">
+      <c r="A79" s="1">
+        <v>0</v>
+      </c>
+      <c r="F79" s="1">
+        <v>4</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>0</v>
+      </c>
+      <c r="O79" s="1">
+        <v>4</v>
+      </c>
+      <c r="S79" s="1">
+        <v>4</v>
+      </c>
+      <c r="W79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23">
+      <c r="A80" s="1">
+        <v>0</v>
+      </c>
+      <c r="B80" s="1">
+        <v>0</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0</v>
+      </c>
+      <c r="D80" s="1">
+        <v>0</v>
+      </c>
+      <c r="E80" s="1">
+        <v>4</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1">
+        <v>0</v>
+      </c>
+      <c r="K80" s="1">
+        <v>0</v>
+      </c>
+      <c r="M80" s="1">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>4</v>
+      </c>
+      <c r="V80" s="1">
+        <v>4</v>
+      </c>
+      <c r="W80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23">
+      <c r="A81" s="1">
+        <v>0</v>
+      </c>
+      <c r="B81" s="1">
+        <v>0</v>
+      </c>
+      <c r="C81" s="1">
+        <v>0</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1">
+        <v>0</v>
+      </c>
+      <c r="K81" s="1">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1">
+        <v>0</v>
+      </c>
+      <c r="O81" s="1">
+        <v>0</v>
+      </c>
+      <c r="P81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>0</v>
+      </c>
+      <c r="R81" s="1">
+        <v>0</v>
+      </c>
+      <c r="T81" s="1">
+        <v>4</v>
+      </c>
+      <c r="U81" s="1">
+        <v>0</v>
+      </c>
+      <c r="V81" s="1">
+        <v>0</v>
+      </c>
+      <c r="W81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23">
+      <c r="A82" s="1">
+        <v>0</v>
+      </c>
+      <c r="B82" s="1">
+        <v>0</v>
+      </c>
+      <c r="C82" s="1">
+        <v>0</v>
+      </c>
+      <c r="D82" s="1">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1">
+        <v>0</v>
+      </c>
+      <c r="K82" s="1">
+        <v>0</v>
+      </c>
+      <c r="M82" s="1">
+        <v>0</v>
+      </c>
+      <c r="N82" s="1">
+        <v>0</v>
+      </c>
+      <c r="O82" s="1">
+        <v>0</v>
+      </c>
+      <c r="P82" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>0</v>
+      </c>
+      <c r="R82" s="1">
+        <v>0</v>
+      </c>
+      <c r="U82" s="1">
+        <v>0</v>
+      </c>
+      <c r="V82" s="1">
+        <v>0</v>
+      </c>
+      <c r="W82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23">
+      <c r="A83" s="1">
+        <v>0</v>
+      </c>
+      <c r="F83" s="1">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1">
+        <v>2</v>
+      </c>
+      <c r="K83" s="1">
+        <v>0</v>
+      </c>
+      <c r="M83" s="1">
+        <v>0</v>
+      </c>
+      <c r="N83" s="1">
+        <v>0</v>
+      </c>
+      <c r="O83" s="1">
+        <v>0</v>
+      </c>
+      <c r="P83" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="1">
+        <v>0</v>
+      </c>
+      <c r="R83" s="1">
+        <v>0</v>
+      </c>
+      <c r="U83" s="1">
+        <v>0</v>
+      </c>
+      <c r="V83" s="1">
+        <v>0</v>
+      </c>
+      <c r="W83" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23">
+      <c r="A84" s="1">
+        <v>0</v>
+      </c>
+      <c r="B84" s="1">
+        <v>0</v>
+      </c>
+      <c r="C84" s="1">
+        <v>0</v>
+      </c>
+      <c r="D84" s="1">
+        <v>0</v>
+      </c>
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1">
+        <v>0</v>
+      </c>
+      <c r="M84" s="1">
+        <v>0</v>
+      </c>
+      <c r="N84" s="1">
+        <v>0</v>
+      </c>
+      <c r="O84" s="1">
+        <v>0</v>
+      </c>
+      <c r="P84" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="1">
+        <v>0</v>
+      </c>
+      <c r="R84" s="1">
+        <v>0</v>
+      </c>
+      <c r="S84" s="1">
+        <v>0</v>
+      </c>
+      <c r="T84" s="1">
+        <v>0</v>
+      </c>
+      <c r="U84" s="1">
+        <v>0</v>
+      </c>
+      <c r="V84" s="1">
+        <v>0</v>
+      </c>
+      <c r="W84" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="4" priority="2">
+  <conditionalFormatting sqref="A1:XFD1000">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+      <formula>4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>MOD(ROW(),12)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="3" priority="10">
       <formula>AND(A1=0,A1&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="11" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="12" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/CSV/StageMove.xlsx
+++ b/Data/CSV/StageMove.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Class\VocationalSchoolData\Programing\SpringContest\SpringContest_26\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469903D3-D6FA-4008-AE54-0D0475EC8411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D536FA0C-D1DF-47FF-840D-ECBBFE97FC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3337,9 +3337,6 @@
       <c r="B65" s="1">
         <v>0</v>
       </c>
-      <c r="C65" s="1">
-        <v>1</v>
-      </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
@@ -3360,6 +3357,9 @@
       </c>
       <c r="N65" s="1">
         <v>0</v>
+      </c>
+      <c r="P65" s="1">
+        <v>4</v>
       </c>
       <c r="Q65" s="1">
         <v>0</v>
@@ -3405,12 +3405,6 @@
       <c r="M66" s="1">
         <v>0</v>
       </c>
-      <c r="N66" s="1">
-        <v>4</v>
-      </c>
-      <c r="S66" s="1">
-        <v>4</v>
-      </c>
       <c r="W66" s="1">
         <v>0</v>
       </c>
@@ -3428,12 +3422,6 @@
       <c r="M67" s="1">
         <v>0</v>
       </c>
-      <c r="N67" s="1">
-        <v>4</v>
-      </c>
-      <c r="P67" s="1">
-        <v>4</v>
-      </c>
       <c r="W67" s="1">
         <v>0</v>
       </c>
@@ -3442,6 +3430,9 @@
       <c r="A68" s="1">
         <v>0</v>
       </c>
+      <c r="B68" s="1">
+        <v>1</v>
+      </c>
       <c r="C68" s="1">
         <v>4</v>
       </c>
@@ -3516,9 +3507,6 @@
       <c r="T69" s="1">
         <v>0</v>
       </c>
-      <c r="V69" s="1">
-        <v>4</v>
-      </c>
       <c r="W69" s="1">
         <v>0</v>
       </c>
@@ -3600,9 +3588,6 @@
       </c>
       <c r="S71" s="1">
         <v>3</v>
-      </c>
-      <c r="T71" s="1">
-        <v>4</v>
       </c>
       <c r="V71" s="1">
         <v>4</v>

--- a/Data/CSV/StageMove.xlsx
+++ b/Data/CSV/StageMove.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Class\VocationalSchoolData\Programing\SpringContest\SpringContest_26\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0670A46-6B59-4ED3-82E7-BD443D5191D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32B6661-FA5E-48D1-A578-9766CEA7E490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,27 +105,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF005500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA50000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color theme="0"/>
@@ -186,21 +166,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF005500"/>
         </patternFill>
       </fill>
     </dxf>
@@ -210,27 +176,7 @@
       </font>
       <fill>
         <patternFill>
-          <fgColor auto="1"/>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="dashDot">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8A0000"/>
+          <bgColor rgb="FFA50000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1778,9 +1724,6 @@
       <c r="I29" s="1">
         <v>0</v>
       </c>
-      <c r="J29" s="1">
-        <v>4</v>
-      </c>
       <c r="K29" s="1">
         <v>0</v>
       </c>
@@ -3487,6 +3430,9 @@
       <c r="D66" s="1">
         <v>4</v>
       </c>
+      <c r="F66" s="1">
+        <v>6</v>
+      </c>
       <c r="H66" s="1">
         <v>4</v>
       </c>
@@ -3507,8 +3453,14 @@
       <c r="A67" s="1">
         <v>0</v>
       </c>
+      <c r="B67" s="1">
+        <v>1</v>
+      </c>
       <c r="F67" s="1">
         <v>4</v>
+      </c>
+      <c r="G67" s="1">
+        <v>6</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
@@ -3527,17 +3479,11 @@
       <c r="A68" s="1">
         <v>0</v>
       </c>
-      <c r="B68" s="1">
-        <v>1</v>
-      </c>
       <c r="C68" s="1">
         <v>4</v>
       </c>
       <c r="D68" s="1">
         <v>4</v>
-      </c>
-      <c r="G68" s="1">
-        <v>5</v>
       </c>
       <c r="H68" s="1">
         <v>4</v>
@@ -3575,13 +3521,13 @@
         <v>0</v>
       </c>
       <c r="B69" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F69" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
@@ -3616,19 +3562,19 @@
         <v>0</v>
       </c>
       <c r="B70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H70" s="1">
         <v>3</v>
       </c>
       <c r="J70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
@@ -3657,16 +3603,16 @@
         <v>0</v>
       </c>
       <c r="C71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
@@ -4340,29 +4286,29 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1000">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="11">
+    <cfRule type="expression" dxfId="4" priority="11">
       <formula>MOD(ROW(),12)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="12">
+    <cfRule type="expression" dxfId="3" priority="12">
       <formula>AND(A1=0,A1&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
       <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>5</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/CSV/StageMove.xlsx
+++ b/Data/CSV/StageMove.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Class\VocationalSchoolData\Programing\SpringContest\SpringContest_26\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32B6661-FA5E-48D1-A578-9766CEA7E490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1095CD57-AD6C-44AA-800D-F0B276C6CED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1226,9 +1226,6 @@
       <c r="P17" s="1">
         <v>0</v>
       </c>
-      <c r="Q17" s="1">
-        <v>4</v>
-      </c>
       <c r="T17" s="1">
         <v>0</v>
       </c>
@@ -1263,6 +1260,9 @@
       </c>
       <c r="P18" s="1">
         <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>4</v>
       </c>
       <c r="R18" s="1">
         <v>4</v>
@@ -3424,20 +3424,8 @@
       <c r="A66" s="1">
         <v>0</v>
       </c>
-      <c r="B66" s="1">
-        <v>4</v>
-      </c>
-      <c r="D66" s="1">
-        <v>4</v>
-      </c>
       <c r="F66" s="1">
         <v>6</v>
-      </c>
-      <c r="H66" s="1">
-        <v>4</v>
-      </c>
-      <c r="J66" s="1">
-        <v>4</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
@@ -3813,9 +3801,6 @@
       </c>
       <c r="O75" s="1">
         <v>3</v>
-      </c>
-      <c r="P75" s="1">
-        <v>4</v>
       </c>
       <c r="Q75" s="1">
         <v>0</v>
